--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -414,17 +414,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07/01/26</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D4">
-        <v>10</v>
+      <c r="D5">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -434,7 +450,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -470,6 +486,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>07/01/26</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -496,7 +517,10 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -523,6 +547,9 @@
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -548,6 +575,9 @@
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -573,6 +603,9 @@
       <c r="G5">
         <v>0</v>
       </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -598,6 +631,9 @@
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -621,6 +657,9 @@
         <v>0</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>1</v>
       </c>
     </row>
@@ -646,6 +685,9 @@
         <v>0</v>
       </c>
       <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>1</v>
       </c>
     </row>
@@ -671,6 +713,9 @@
         <v>0</v>
       </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>1</v>
       </c>
     </row>
@@ -698,6 +743,9 @@
       <c r="G10">
         <v>0</v>
       </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -721,6 +769,9 @@
         <v>0</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>1</v>
       </c>
     </row>
@@ -746,6 +797,9 @@
         <v>0</v>
       </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>1</v>
       </c>
     </row>
@@ -771,6 +825,9 @@
         <v>0</v>
       </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>17</v>
       </c>
     </row>
@@ -796,7 +853,10 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -853,7 +913,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -868,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -1153,7 +1213,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>16</v>
@@ -1168,7 +1228,7 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1178,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1924,6 +1984,28 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>07/01/26</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,6 +375,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -392,6 +397,9 @@
         <v>5</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>8</v>
       </c>
     </row>
@@ -408,6 +416,9 @@
         <v>2</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
     </row>
@@ -424,23 +435,67 @@
         <v>0</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/02/26</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>07/03/26</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B7">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="C7">
         <v>7</v>
       </c>
-      <c r="D5">
-        <v>11</v>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -450,7 +505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -491,6 +546,16 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>07/02/26</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>07/03/26</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -520,7 +585,13 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -550,6 +621,12 @@
       <c r="H3">
         <v>0</v>
       </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -578,6 +655,12 @@
       <c r="H4">
         <v>0</v>
       </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -606,6 +689,12 @@
       <c r="H5">
         <v>0</v>
       </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -634,6 +723,12 @@
       <c r="H6">
         <v>0</v>
       </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -660,6 +755,12 @@
         <v>0</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -688,6 +789,12 @@
         <v>0</v>
       </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <v>1</v>
       </c>
     </row>
@@ -716,6 +823,12 @@
         <v>0</v>
       </c>
       <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>1</v>
       </c>
     </row>
@@ -746,6 +859,12 @@
       <c r="H10">
         <v>0</v>
       </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -772,6 +891,12 @@
         <v>0</v>
       </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>1</v>
       </c>
     </row>
@@ -800,6 +925,12 @@
         <v>0</v>
       </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <v>1</v>
       </c>
     </row>
@@ -828,6 +959,12 @@
         <v>0</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <v>17</v>
       </c>
     </row>
@@ -856,7 +993,13 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -897,10 +1040,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>TE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -925,10 +1073,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -955,6 +1106,9 @@
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -980,6 +1134,9 @@
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1005,6 +1162,9 @@
       <c r="G5">
         <v>0</v>
       </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1030,6 +1190,9 @@
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1053,6 +1216,9 @@
         <v>0</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>1</v>
       </c>
     </row>
@@ -1075,9 +1241,12 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>1</v>
       </c>
     </row>
@@ -1100,9 +1269,12 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
         <v>1</v>
       </c>
     </row>
@@ -1130,6 +1302,9 @@
       <c r="G10">
         <v>0</v>
       </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1150,9 +1325,12 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
         <v>1</v>
       </c>
     </row>
@@ -1175,9 +1353,12 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>1</v>
       </c>
     </row>
@@ -1203,6 +1384,9 @@
         <v>0</v>
       </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>17</v>
       </c>
     </row>
@@ -1225,10 +1409,13 @@
         <v>1</v>
       </c>
       <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
         <v>4</v>
       </c>
-      <c r="G14">
-        <v>33</v>
+      <c r="H14">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2006,6 +2193,72 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>07/03/26</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>07/03/26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>07/02/26</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -365,20 +365,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JS</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>NB</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -391,15 +396,18 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>3</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>8</v>
       </c>
     </row>
@@ -413,12 +421,15 @@
         <v>0</v>
       </c>
       <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>2</v>
       </c>
     </row>
@@ -429,15 +440,18 @@
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
     </row>
@@ -448,16 +462,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -473,29 +490,57 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/06/26</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="D8">
         <v>7</v>
       </c>
-      <c r="D7">
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="E7">
-        <v>14</v>
+      <c r="F8">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -505,7 +550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -556,6 +601,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>07/06/26</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -585,13 +635,16 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -627,6 +680,9 @@
       <c r="J3">
         <v>0</v>
       </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -661,6 +717,9 @@
       <c r="J4">
         <v>0</v>
       </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -695,6 +754,9 @@
       <c r="J5">
         <v>0</v>
       </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -729,6 +791,9 @@
       <c r="J6">
         <v>0</v>
       </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -761,6 +826,9 @@
         <v>0</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -795,6 +863,9 @@
         <v>0</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>1</v>
       </c>
     </row>
@@ -829,6 +900,9 @@
         <v>0</v>
       </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>1</v>
       </c>
     </row>
@@ -865,6 +939,9 @@
       <c r="J10">
         <v>0</v>
       </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -897,6 +974,9 @@
         <v>0</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>1</v>
       </c>
     </row>
@@ -931,6 +1011,9 @@
         <v>0</v>
       </c>
       <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>1</v>
       </c>
     </row>
@@ -965,6 +1048,9 @@
         <v>0</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>17</v>
       </c>
     </row>
@@ -993,13 +1079,16 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
       <c r="J14">
-        <v>36</v>
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1009,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1020,35 +1109,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>JS</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>JV</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>NB</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1061,25 +1155,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1109,6 +1206,9 @@
       <c r="H3">
         <v>0</v>
       </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1137,6 +1237,9 @@
       <c r="H4">
         <v>0</v>
       </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1165,6 +1268,9 @@
       <c r="H5">
         <v>0</v>
       </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1193,6 +1299,9 @@
       <c r="H6">
         <v>0</v>
       </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1210,15 +1319,18 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
@@ -1244,9 +1356,12 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>1</v>
       </c>
     </row>
@@ -1272,9 +1387,12 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <v>1</v>
       </c>
     </row>
@@ -1305,6 +1423,9 @@
       <c r="H10">
         <v>0</v>
       </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1328,9 +1449,12 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
         <v>1</v>
       </c>
     </row>
@@ -1356,9 +1480,12 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>1</v>
       </c>
     </row>
@@ -1372,13 +1499,13 @@
         <v>0</v>
       </c>
       <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>16</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1387,6 +1514,9 @@
         <v>0</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>17</v>
       </c>
     </row>
@@ -1397,25 +1527,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
         <v>4</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>16</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>8</v>
       </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
       <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
         <v>3</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>4</v>
       </c>
-      <c r="H14">
-        <v>36</v>
+      <c r="I14">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2259,6 +2392,116 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>07/02/26</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>07/02/26</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>07/02/26</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>07/06/26</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>07/06/26</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -408,6 +413,9 @@
         <v>0</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>8</v>
       </c>
     </row>
@@ -430,6 +438,9 @@
         <v>0</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>
@@ -452,6 +463,9 @@
         <v>0</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
@@ -474,6 +488,9 @@
         <v>1</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>4</v>
       </c>
     </row>
@@ -496,6 +513,9 @@
         <v>2</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>2</v>
       </c>
     </row>
@@ -518,29 +538,85 @@
         <v>0</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/07/26</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B10">
         <v>5</v>
       </c>
-      <c r="C8">
+      <c r="C10">
         <v>4</v>
       </c>
-      <c r="D8">
+      <c r="D10">
         <v>7</v>
       </c>
-      <c r="E8">
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F8">
-        <v>19</v>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -550,7 +626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -606,6 +682,16 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>07/07/26</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -644,7 +730,13 @@
         <v>2</v>
       </c>
       <c r="K2">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -683,6 +775,12 @@
       <c r="K3">
         <v>0</v>
       </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -720,6 +818,12 @@
       <c r="K4">
         <v>0</v>
       </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -757,6 +861,12 @@
       <c r="K5">
         <v>0</v>
       </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -794,6 +904,12 @@
       <c r="K6">
         <v>0</v>
       </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -829,6 +945,12 @@
         <v>0</v>
       </c>
       <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>1</v>
       </c>
     </row>
@@ -866,6 +988,12 @@
         <v>0</v>
       </c>
       <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <v>1</v>
       </c>
     </row>
@@ -903,6 +1031,12 @@
         <v>0</v>
       </c>
       <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>1</v>
       </c>
     </row>
@@ -942,6 +1076,12 @@
       <c r="K10">
         <v>0</v>
       </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -977,6 +1117,12 @@
         <v>0</v>
       </c>
       <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>1</v>
       </c>
     </row>
@@ -1014,6 +1160,12 @@
         <v>0</v>
       </c>
       <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>1</v>
       </c>
     </row>
@@ -1051,6 +1203,12 @@
         <v>0</v>
       </c>
       <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>17</v>
       </c>
     </row>
@@ -1088,7 +1246,13 @@
         <v>2</v>
       </c>
       <c r="K14">
-        <v>41</v>
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1139,10 +1303,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>TE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1173,10 +1342,13 @@
         <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1209,6 +1381,9 @@
       <c r="I3">
         <v>0</v>
       </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1240,6 +1415,9 @@
       <c r="I4">
         <v>0</v>
       </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1271,6 +1449,9 @@
       <c r="I5">
         <v>0</v>
       </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1302,6 +1483,9 @@
       <c r="I6">
         <v>0</v>
       </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1331,6 +1515,9 @@
         <v>0</v>
       </c>
       <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>1</v>
       </c>
     </row>
@@ -1359,9 +1546,12 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
         <v>1</v>
       </c>
     </row>
@@ -1390,9 +1580,12 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
         <v>1</v>
       </c>
     </row>
@@ -1426,6 +1619,9 @@
       <c r="I10">
         <v>0</v>
       </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1452,9 +1648,12 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
         <v>1</v>
       </c>
     </row>
@@ -1483,9 +1682,12 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
         <v>1</v>
       </c>
     </row>
@@ -1517,6 +1719,9 @@
         <v>0</v>
       </c>
       <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <v>17</v>
       </c>
     </row>
@@ -1545,10 +1750,13 @@
         <v>3</v>
       </c>
       <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
         <v>4</v>
       </c>
-      <c r="I14">
-        <v>41</v>
+      <c r="J14">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1558,7 +1766,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2502,6 +2710,89 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>07/07/26</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>07/07/26</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T_Store999</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>07/07/26</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -597,26 +597,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>5</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>4</v>
       </c>
-      <c r="D10">
-        <v>7</v>
-      </c>
-      <c r="E10">
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
         <v>3</v>
       </c>
-      <c r="F10">
+      <c r="F11">
         <v>3</v>
       </c>
-      <c r="G10">
-        <v>22</v>
+      <c r="G11">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +651,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -692,6 +717,11 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -736,7 +766,10 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -781,6 +814,9 @@
       <c r="M3">
         <v>0</v>
       </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -824,6 +860,9 @@
       <c r="M4">
         <v>0</v>
       </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -867,6 +906,9 @@
       <c r="M5">
         <v>0</v>
       </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -910,6 +952,9 @@
       <c r="M6">
         <v>0</v>
       </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -951,7 +996,10 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="N7">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -994,6 +1042,9 @@
         <v>0</v>
       </c>
       <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
         <v>1</v>
       </c>
     </row>
@@ -1037,6 +1088,9 @@
         <v>0</v>
       </c>
       <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
         <v>1</v>
       </c>
     </row>
@@ -1082,6 +1136,9 @@
       <c r="M10">
         <v>0</v>
       </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1123,7 +1180,10 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="N11">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1166,6 +1226,9 @@
         <v>0</v>
       </c>
       <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>1</v>
       </c>
     </row>
@@ -1209,6 +1272,9 @@
         <v>0</v>
       </c>
       <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>17</v>
       </c>
     </row>
@@ -1252,7 +1318,10 @@
         <v>1</v>
       </c>
       <c r="M14">
-        <v>44</v>
+        <v>8</v>
+      </c>
+      <c r="N14">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1333,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1348,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1503,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1518,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1639,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1654,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1741,7 +1810,7 @@
         <v>16</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1756,7 +1825,7 @@
         <v>4</v>
       </c>
       <c r="J14">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1766,7 +1835,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2793,6 +2862,182 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10595</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10132</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10131</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10119</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10602</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10286</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10670</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10669</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>07/13/26</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -622,26 +622,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07/14/26</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>5</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>4</v>
       </c>
-      <c r="D11">
-        <v>8</v>
-      </c>
-      <c r="E11">
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12">
         <v>3</v>
       </c>
-      <c r="F11">
+      <c r="F12">
         <v>3</v>
       </c>
-      <c r="G11">
-        <v>23</v>
+      <c r="G12">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -651,7 +676,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -722,6 +747,11 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>07/14/26</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -769,7 +799,10 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -817,6 +850,9 @@
       <c r="N3">
         <v>0</v>
       </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -863,6 +899,9 @@
       <c r="N4">
         <v>0</v>
       </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -909,6 +948,9 @@
       <c r="N5">
         <v>0</v>
       </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -955,6 +997,9 @@
       <c r="N6">
         <v>0</v>
       </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -999,6 +1044,9 @@
         <v>4</v>
       </c>
       <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <v>5</v>
       </c>
     </row>
@@ -1045,6 +1093,9 @@
         <v>0</v>
       </c>
       <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
         <v>1</v>
       </c>
     </row>
@@ -1091,6 +1142,9 @@
         <v>0</v>
       </c>
       <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
         <v>1</v>
       </c>
     </row>
@@ -1139,6 +1193,9 @@
       <c r="N10">
         <v>0</v>
       </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1183,6 +1240,9 @@
         <v>3</v>
       </c>
       <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
         <v>4</v>
       </c>
     </row>
@@ -1229,6 +1289,9 @@
         <v>0</v>
       </c>
       <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
         <v>1</v>
       </c>
     </row>
@@ -1275,6 +1338,9 @@
         <v>0</v>
       </c>
       <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
         <v>17</v>
       </c>
     </row>
@@ -1321,7 +1387,10 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>52</v>
+        <v>3</v>
+      </c>
+      <c r="O14">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1402,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1417,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -1810,7 +1879,7 @@
         <v>16</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1825,7 +1894,7 @@
         <v>4</v>
       </c>
       <c r="J14">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1835,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3038,6 +3107,72 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10249</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>07/14/26</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10039</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>07/14/26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>10183</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>07/14/26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -403,14 +403,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07/16/26</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -420,7 +433,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -441,6 +454,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>07/16/26</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -458,7 +476,10 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -476,6 +497,9 @@
       <c r="D3">
         <v>0</v>
       </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -492,6 +516,9 @@
       <c r="D4">
         <v>0</v>
       </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -508,6 +535,9 @@
       <c r="D5">
         <v>0</v>
       </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -524,6 +554,9 @@
       <c r="D6">
         <v>0</v>
       </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -538,6 +571,9 @@
         <v>0</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>4</v>
       </c>
     </row>
@@ -556,6 +592,9 @@
       <c r="D8">
         <v>0</v>
       </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -572,6 +611,9 @@
       <c r="D9">
         <v>0</v>
       </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -588,6 +630,9 @@
       <c r="D10">
         <v>0</v>
       </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -602,6 +647,9 @@
         <v>0</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>3</v>
       </c>
     </row>
@@ -620,6 +668,9 @@
       <c r="D12">
         <v>0</v>
       </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -636,6 +687,9 @@
       <c r="D13">
         <v>0</v>
       </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -650,7 +704,10 @@
         <v>3</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -687,10 +744,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -843,10 +900,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -856,7 +913,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1101,6 +1158,66 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13">
+        <v>10027</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07/16/26</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>10242</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07/16/26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>10128</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07/16/26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -416,14 +416,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/17/26</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -433,7 +446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -459,6 +472,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>07/17/26</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -479,7 +497,10 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -500,6 +521,9 @@
       <c r="E3">
         <v>0</v>
       </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -519,6 +543,9 @@
       <c r="E4">
         <v>0</v>
       </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -538,6 +565,9 @@
       <c r="E5">
         <v>0</v>
       </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -557,6 +587,9 @@
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -574,6 +607,9 @@
         <v>0</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>4</v>
       </c>
     </row>
@@ -595,6 +631,9 @@
       <c r="E8">
         <v>0</v>
       </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -614,6 +653,9 @@
       <c r="E9">
         <v>0</v>
       </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -633,6 +675,9 @@
       <c r="E10">
         <v>0</v>
       </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -650,6 +695,9 @@
         <v>0</v>
       </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>3</v>
       </c>
     </row>
@@ -671,6 +719,9 @@
       <c r="E12">
         <v>0</v>
       </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -690,6 +741,9 @@
       <c r="E13">
         <v>0</v>
       </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -707,7 +761,10 @@
         <v>3</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -744,10 +801,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -900,10 +957,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +970,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1218,6 +1275,46 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16">
+        <v>10104</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07/17/26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>10052</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07/17/26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -429,14 +429,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/18/26</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>9</v>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -446,7 +459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -477,6 +490,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>07/18/26</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -500,7 +518,10 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -524,6 +545,9 @@
       <c r="F3">
         <v>0</v>
       </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -546,6 +570,9 @@
       <c r="F4">
         <v>0</v>
       </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -568,6 +595,9 @@
       <c r="F5">
         <v>0</v>
       </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -590,6 +620,9 @@
       <c r="F6">
         <v>0</v>
       </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -610,6 +643,9 @@
         <v>0</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>4</v>
       </c>
     </row>
@@ -634,6 +670,9 @@
       <c r="F8">
         <v>0</v>
       </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -656,6 +695,9 @@
       <c r="F9">
         <v>0</v>
       </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -678,6 +720,9 @@
       <c r="F10">
         <v>0</v>
       </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +743,9 @@
         <v>0</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>3</v>
       </c>
     </row>
@@ -722,6 +770,9 @@
       <c r="F12">
         <v>0</v>
       </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,6 +795,9 @@
       <c r="F13">
         <v>0</v>
       </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -764,7 +818,10 @@
         <v>2</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -801,10 +858,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -957,10 +1014,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1315,6 +1372,26 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18">
+        <v>10314</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07/18/26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -365,10 +365,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -381,11 +386,14 @@
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -394,11 +402,14 @@
         </is>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -407,11 +418,14 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -420,11 +434,14 @@
         </is>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -433,23 +450,45 @@
         </is>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>10</v>
+      <c r="D8">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -459,7 +498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -495,6 +534,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -521,7 +565,10 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -548,6 +595,9 @@
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -573,6 +623,9 @@
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -598,6 +651,9 @@
       <c r="G5">
         <v>0</v>
       </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -623,6 +679,9 @@
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -646,6 +705,9 @@
         <v>0</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>4</v>
       </c>
     </row>
@@ -673,6 +735,9 @@
       <c r="G8">
         <v>0</v>
       </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -698,6 +763,9 @@
       <c r="G9">
         <v>0</v>
       </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -723,6 +791,9 @@
       <c r="G10">
         <v>0</v>
       </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -746,6 +817,9 @@
         <v>0</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>3</v>
       </c>
     </row>
@@ -773,6 +847,9 @@
       <c r="G12">
         <v>0</v>
       </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -798,6 +875,9 @@
       <c r="G13">
         <v>0</v>
       </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -821,7 +901,10 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -831,7 +914,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -842,10 +925,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -858,11 +946,14 @@
         </is>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -876,6 +967,9 @@
       <c r="C3">
         <v>0</v>
       </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -889,6 +983,9 @@
       <c r="C4">
         <v>0</v>
       </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -902,6 +999,9 @@
       <c r="C5">
         <v>0</v>
       </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -915,6 +1015,9 @@
       <c r="C6">
         <v>0</v>
       </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -923,11 +1026,14 @@
         </is>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -941,6 +1047,9 @@
       <c r="C8">
         <v>0</v>
       </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -954,6 +1063,9 @@
       <c r="C9">
         <v>0</v>
       </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -967,6 +1079,9 @@
       <c r="C10">
         <v>0</v>
       </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -975,11 +1090,14 @@
         </is>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -993,6 +1111,9 @@
       <c r="C12">
         <v>0</v>
       </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1006,6 +1127,9 @@
       <c r="C13">
         <v>0</v>
       </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1014,10 +1138,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>17</v>
+      </c>
+      <c r="D14">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1027,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1392,6 +1519,106 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19">
+        <v>10272</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10400</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10080</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>10179</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>10659</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -469,26 +469,42 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/21/26</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>5</v>
       </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
+      <c r="C9">
         <v>15</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -498,7 +514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -539,6 +555,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>07/21/26</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -565,10 +586,13 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -598,6 +622,9 @@
       <c r="H3">
         <v>0</v>
       </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -626,6 +653,9 @@
       <c r="H4">
         <v>0</v>
       </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -654,6 +684,9 @@
       <c r="H5">
         <v>0</v>
       </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -682,6 +715,9 @@
       <c r="H6">
         <v>0</v>
       </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -708,6 +744,9 @@
         <v>0</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>4</v>
       </c>
     </row>
@@ -738,6 +777,9 @@
       <c r="H8">
         <v>0</v>
       </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -766,6 +808,9 @@
       <c r="H9">
         <v>0</v>
       </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -794,6 +839,9 @@
       <c r="H10">
         <v>0</v>
       </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -820,6 +868,9 @@
         <v>0</v>
       </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>3</v>
       </c>
     </row>
@@ -850,6 +901,9 @@
       <c r="H12">
         <v>0</v>
       </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -878,6 +932,9 @@
       <c r="H13">
         <v>0</v>
       </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -901,10 +958,13 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H14">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -949,10 +1009,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -1141,10 +1201,10 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D14">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1619,6 +1679,121 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24">
+        <v>10279</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>10171</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>10366</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>07/21/26</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>10169</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>10029</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>07/21/26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>10279</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>07/20/26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -494,17 +494,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07/23/26</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>5</v>
       </c>
-      <c r="C9">
-        <v>15</v>
-      </c>
-      <c r="D9">
-        <v>20</v>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -514,7 +530,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -560,6 +576,11 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>07/23/26</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -592,7 +613,10 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -625,6 +649,9 @@
       <c r="I3">
         <v>0</v>
       </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -656,6 +683,9 @@
       <c r="I4">
         <v>0</v>
       </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -687,6 +717,9 @@
       <c r="I5">
         <v>0</v>
       </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -718,6 +751,9 @@
       <c r="I6">
         <v>0</v>
       </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -747,6 +783,9 @@
         <v>0</v>
       </c>
       <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>4</v>
       </c>
     </row>
@@ -780,6 +819,9 @@
       <c r="I8">
         <v>0</v>
       </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -811,6 +853,9 @@
       <c r="I9">
         <v>0</v>
       </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -842,6 +887,9 @@
       <c r="I10">
         <v>0</v>
       </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -871,6 +919,9 @@
         <v>0</v>
       </c>
       <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>3</v>
       </c>
     </row>
@@ -904,6 +955,9 @@
       <c r="I12">
         <v>0</v>
       </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -935,6 +989,9 @@
       <c r="I13">
         <v>0</v>
       </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -964,7 +1021,10 @@
         <v>2</v>
       </c>
       <c r="I14">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="J14">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1009,10 +1069,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1201,10 +1261,10 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1794,6 +1854,66 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30">
+        <v>10016</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>07/23/26</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>10111</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>07/23/26</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>10188</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>07/23/26</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -722,23 +722,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>08/03/26</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>16</v>
       </c>
-      <c r="C17">
-        <v>24</v>
-      </c>
-      <c r="D17">
+      <c r="C18">
+        <v>25</v>
+      </c>
+      <c r="D18">
         <v>28</v>
       </c>
-      <c r="E17">
+      <c r="E18">
         <v>9</v>
       </c>
-      <c r="F17">
-        <v>77</v>
+      <c r="F18">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -748,7 +770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -834,6 +856,11 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>08/03/26</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -890,7 +917,10 @@
         <v>7</v>
       </c>
       <c r="Q2">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -945,6 +975,9 @@
         <v>0</v>
       </c>
       <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
         <v>1</v>
       </c>
     </row>
@@ -1002,6 +1035,9 @@
       <c r="Q4">
         <v>0</v>
       </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1057,6 +1093,9 @@
       <c r="Q5">
         <v>0</v>
       </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1112,6 +1151,9 @@
       <c r="Q6">
         <v>0</v>
       </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1165,6 +1207,9 @@
         <v>0</v>
       </c>
       <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <v>8</v>
       </c>
     </row>
@@ -1220,6 +1265,9 @@
         <v>0</v>
       </c>
       <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
         <v>1</v>
       </c>
     </row>
@@ -1277,6 +1325,9 @@
       <c r="Q9">
         <v>0</v>
       </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1332,6 +1383,9 @@
       <c r="Q10">
         <v>0</v>
       </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1385,6 +1439,9 @@
         <v>0</v>
       </c>
       <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
         <v>3</v>
       </c>
     </row>
@@ -1440,6 +1497,9 @@
         <v>0</v>
       </c>
       <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
         <v>2</v>
       </c>
     </row>
@@ -1495,6 +1555,9 @@
         <v>0</v>
       </c>
       <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
         <v>1</v>
       </c>
     </row>
@@ -1550,7 +1613,10 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>93</v>
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1605,7 +1671,7 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>28</v>
@@ -1614,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="F2">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -1869,7 +1935,7 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>29</v>
@@ -1878,7 +1944,7 @@
         <v>14</v>
       </c>
       <c r="F14">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4010,6 +4076,28 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>10195</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>08/03/26</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -744,23 +744,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>08/07/26</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B18">
-        <v>16</v>
-      </c>
-      <c r="C18">
-        <v>25</v>
-      </c>
-      <c r="D18">
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>27</v>
+      </c>
+      <c r="D19">
         <v>28</v>
       </c>
-      <c r="E18">
+      <c r="E19">
         <v>9</v>
       </c>
-      <c r="F18">
-        <v>78</v>
+      <c r="F19">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -770,7 +792,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -861,6 +883,11 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>08/07/26</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -920,7 +947,10 @@
         <v>1</v>
       </c>
       <c r="R2">
-        <v>78</v>
+        <v>6</v>
+      </c>
+      <c r="S2">
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -978,6 +1008,9 @@
         <v>0</v>
       </c>
       <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>1</v>
       </c>
     </row>
@@ -1038,6 +1071,9 @@
       <c r="R4">
         <v>0</v>
       </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1096,6 +1132,9 @@
       <c r="R5">
         <v>0</v>
       </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1154,6 +1193,9 @@
       <c r="R6">
         <v>0</v>
       </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1210,6 +1252,9 @@
         <v>0</v>
       </c>
       <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>8</v>
       </c>
     </row>
@@ -1268,6 +1313,9 @@
         <v>0</v>
       </c>
       <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>1</v>
       </c>
     </row>
@@ -1328,6 +1376,9 @@
       <c r="R9">
         <v>0</v>
       </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1386,6 +1437,9 @@
       <c r="R10">
         <v>0</v>
       </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1442,7 +1496,10 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1500,6 +1557,9 @@
         <v>0</v>
       </c>
       <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>2</v>
       </c>
     </row>
@@ -1558,6 +1618,9 @@
         <v>0</v>
       </c>
       <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>1</v>
       </c>
     </row>
@@ -1616,7 +1679,10 @@
         <v>1</v>
       </c>
       <c r="R14">
-        <v>94</v>
+        <v>7</v>
+      </c>
+      <c r="S14">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1668,10 +1734,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>28</v>
@@ -1680,7 +1746,7 @@
         <v>9</v>
       </c>
       <c r="F2">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -1866,7 +1932,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -1878,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1932,10 +1998,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>29</v>
@@ -1944,7 +2010,7 @@
         <v>14</v>
       </c>
       <c r="F14">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1954,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4098,6 +4164,160 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>08/07/26</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>10226</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>08/07/26</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>08/07/26</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>10273</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>08/07/26</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>10129</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>08/07/26</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>10151</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>08/07/26</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>10087</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>08/07/26</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -766,23 +766,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>08/10/26</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>20</v>
       </c>
-      <c r="C19">
-        <v>27</v>
-      </c>
-      <c r="D19">
+      <c r="C20">
+        <v>29</v>
+      </c>
+      <c r="D20">
         <v>28</v>
       </c>
-      <c r="E19">
+      <c r="E20">
         <v>9</v>
       </c>
-      <c r="F19">
-        <v>84</v>
+      <c r="F20">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -792,7 +814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -888,6 +910,11 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>08/10/26</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -950,7 +977,10 @@
         <v>6</v>
       </c>
       <c r="S2">
-        <v>84</v>
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -1011,6 +1041,9 @@
         <v>0</v>
       </c>
       <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
         <v>1</v>
       </c>
     </row>
@@ -1074,6 +1107,9 @@
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1135,6 +1171,9 @@
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1196,6 +1235,9 @@
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1255,6 +1297,9 @@
         <v>0</v>
       </c>
       <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>8</v>
       </c>
     </row>
@@ -1316,6 +1361,9 @@
         <v>0</v>
       </c>
       <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>1</v>
       </c>
     </row>
@@ -1379,6 +1427,9 @@
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1440,6 +1491,9 @@
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1499,6 +1553,9 @@
         <v>1</v>
       </c>
       <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
         <v>4</v>
       </c>
     </row>
@@ -1560,6 +1617,9 @@
         <v>0</v>
       </c>
       <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
         <v>2</v>
       </c>
     </row>
@@ -1621,6 +1681,9 @@
         <v>0</v>
       </c>
       <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
         <v>1</v>
       </c>
     </row>
@@ -1682,7 +1745,10 @@
         <v>7</v>
       </c>
       <c r="S14">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="T14">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1737,7 +1803,7 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>28</v>
@@ -1746,7 +1812,7 @@
         <v>9</v>
       </c>
       <c r="F2">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -2001,7 +2067,7 @@
         <v>24</v>
       </c>
       <c r="C14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14">
         <v>29</v>
@@ -2010,7 +2076,7 @@
         <v>14</v>
       </c>
       <c r="F14">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2020,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4318,6 +4384,50 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>10258</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>08/10/26</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>10232</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>08/10/26</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -788,23 +788,67 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>08/11/26</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B20">
-        <v>20</v>
-      </c>
-      <c r="C20">
+      <c r="B22">
+        <v>26</v>
+      </c>
+      <c r="C22">
         <v>29</v>
       </c>
-      <c r="D20">
+      <c r="D22">
         <v>28</v>
       </c>
-      <c r="E20">
+      <c r="E22">
         <v>9</v>
       </c>
-      <c r="F20">
-        <v>86</v>
+      <c r="F22">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -814,7 +858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -915,6 +959,16 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>08/11/26</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -980,7 +1034,13 @@
         <v>2</v>
       </c>
       <c r="T2">
-        <v>86</v>
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>5</v>
+      </c>
+      <c r="V2">
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -1044,6 +1104,12 @@
         <v>0</v>
       </c>
       <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
         <v>1</v>
       </c>
     </row>
@@ -1110,6 +1176,12 @@
       <c r="T4">
         <v>0</v>
       </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1174,6 +1246,12 @@
       <c r="T5">
         <v>0</v>
       </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1238,6 +1316,12 @@
       <c r="T6">
         <v>0</v>
       </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1300,6 +1384,12 @@
         <v>0</v>
       </c>
       <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
         <v>8</v>
       </c>
     </row>
@@ -1364,6 +1454,12 @@
         <v>0</v>
       </c>
       <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
         <v>1</v>
       </c>
     </row>
@@ -1430,6 +1526,12 @@
       <c r="T9">
         <v>0</v>
       </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1494,6 +1596,12 @@
       <c r="T10">
         <v>0</v>
       </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1556,6 +1664,12 @@
         <v>0</v>
       </c>
       <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
         <v>4</v>
       </c>
     </row>
@@ -1620,6 +1734,12 @@
         <v>0</v>
       </c>
       <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
         <v>2</v>
       </c>
     </row>
@@ -1684,6 +1804,12 @@
         <v>0</v>
       </c>
       <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
         <v>1</v>
       </c>
     </row>
@@ -1748,7 +1874,13 @@
         <v>2</v>
       </c>
       <c r="T14">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>5</v>
+      </c>
+      <c r="V14">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1800,7 +1932,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>29</v>
@@ -1812,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="F2">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -2064,7 +2196,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>36</v>
@@ -2076,7 +2208,7 @@
         <v>14</v>
       </c>
       <c r="F14">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2218,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4428,6 +4560,138 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>10069</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>08/11/26</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>10217</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>10178</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>10098</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>10596</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -823,32 +823,54 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>08/14/26</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>7</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>26</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>29</v>
       </c>
-      <c r="D22">
+      <c r="D23">
         <v>28</v>
       </c>
-      <c r="E22">
-        <v>9</v>
-      </c>
-      <c r="F22">
-        <v>92</v>
+      <c r="E23">
+        <v>18</v>
+      </c>
+      <c r="F23">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -858,7 +880,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -969,6 +991,11 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>08/14/26</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1037,10 +1064,13 @@
         <v>1</v>
       </c>
       <c r="U2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V2">
-        <v>92</v>
+        <v>7</v>
+      </c>
+      <c r="W2">
+        <v>101</v>
       </c>
     </row>
     <row r="3">
@@ -1110,6 +1140,9 @@
         <v>0</v>
       </c>
       <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
         <v>1</v>
       </c>
     </row>
@@ -1182,6 +1215,9 @@
       <c r="V4">
         <v>0</v>
       </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1252,6 +1288,9 @@
       <c r="V5">
         <v>0</v>
       </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1322,6 +1361,9 @@
       <c r="V6">
         <v>0</v>
       </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1390,6 +1432,9 @@
         <v>0</v>
       </c>
       <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
         <v>8</v>
       </c>
     </row>
@@ -1460,6 +1505,9 @@
         <v>0</v>
       </c>
       <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
         <v>1</v>
       </c>
     </row>
@@ -1532,6 +1580,9 @@
       <c r="V9">
         <v>0</v>
       </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1602,6 +1653,9 @@
       <c r="V10">
         <v>0</v>
       </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1670,6 +1724,9 @@
         <v>0</v>
       </c>
       <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
         <v>4</v>
       </c>
     </row>
@@ -1740,6 +1797,9 @@
         <v>0</v>
       </c>
       <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
         <v>2</v>
       </c>
     </row>
@@ -1810,6 +1870,9 @@
         <v>0</v>
       </c>
       <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
         <v>1</v>
       </c>
     </row>
@@ -1877,10 +1940,13 @@
         <v>1</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>109</v>
+        <v>7</v>
+      </c>
+      <c r="W14">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1941,10 +2007,10 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
@@ -2205,10 +2271,10 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2218,7 +2284,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4692,6 +4758,204 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>10079</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>08/14/26</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>10121</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>08/14/26</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>10268</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>08/14/26</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>10081</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>08/14/26</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>10076</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>08/14/26</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>10609</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>08/14/26</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>10008</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>10225</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>08/14/26</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -854,23 +854,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>08/16/26</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B23">
-        <v>26</v>
-      </c>
-      <c r="C23">
+      <c r="B24">
+        <v>27</v>
+      </c>
+      <c r="C24">
         <v>29</v>
       </c>
-      <c r="D23">
+      <c r="D24">
         <v>28</v>
       </c>
-      <c r="E23">
+      <c r="E24">
         <v>18</v>
       </c>
-      <c r="F23">
-        <v>101</v>
+      <c r="F24">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -880,7 +902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -996,6 +1018,11 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>08/16/26</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1070,7 +1097,10 @@
         <v>7</v>
       </c>
       <c r="W2">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>102</v>
       </c>
     </row>
     <row r="3">
@@ -1143,6 +1173,9 @@
         <v>0</v>
       </c>
       <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
         <v>1</v>
       </c>
     </row>
@@ -1218,6 +1251,9 @@
       <c r="W4">
         <v>0</v>
       </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1291,6 +1327,9 @@
       <c r="W5">
         <v>0</v>
       </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1364,6 +1403,9 @@
       <c r="W6">
         <v>0</v>
       </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1435,6 +1477,9 @@
         <v>0</v>
       </c>
       <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
         <v>8</v>
       </c>
     </row>
@@ -1508,6 +1553,9 @@
         <v>0</v>
       </c>
       <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
         <v>1</v>
       </c>
     </row>
@@ -1583,6 +1631,9 @@
       <c r="W9">
         <v>0</v>
       </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1656,6 +1707,9 @@
       <c r="W10">
         <v>0</v>
       </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1727,6 +1781,9 @@
         <v>0</v>
       </c>
       <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
         <v>4</v>
       </c>
     </row>
@@ -1800,6 +1857,9 @@
         <v>0</v>
       </c>
       <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
         <v>2</v>
       </c>
     </row>
@@ -1873,6 +1933,9 @@
         <v>0</v>
       </c>
       <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
         <v>1</v>
       </c>
     </row>
@@ -1946,7 +2009,10 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>118</v>
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1998,7 +2064,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>29</v>
@@ -2010,7 +2076,7 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3">
@@ -2262,7 +2328,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14">
         <v>36</v>
@@ -2274,7 +2340,7 @@
         <v>23</v>
       </c>
       <c r="F14">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2284,7 +2350,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4956,6 +5022,28 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>10137</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>08/16/26</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -876,23 +876,45 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B24">
-        <v>27</v>
-      </c>
-      <c r="C24">
-        <v>29</v>
-      </c>
-      <c r="D24">
+      <c r="B25">
+        <v>30</v>
+      </c>
+      <c r="C25">
+        <v>33</v>
+      </c>
+      <c r="D25">
         <v>28</v>
       </c>
-      <c r="E24">
+      <c r="E25">
         <v>18</v>
       </c>
-      <c r="F24">
-        <v>102</v>
+      <c r="F25">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -902,7 +924,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1023,6 +1045,11 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1100,7 +1127,10 @@
         <v>1</v>
       </c>
       <c r="X2">
-        <v>102</v>
+        <v>7</v>
+      </c>
+      <c r="Y2">
+        <v>109</v>
       </c>
     </row>
     <row r="3">
@@ -1176,6 +1206,9 @@
         <v>0</v>
       </c>
       <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
         <v>1</v>
       </c>
     </row>
@@ -1254,6 +1287,9 @@
       <c r="X4">
         <v>0</v>
       </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1330,6 +1366,9 @@
       <c r="X5">
         <v>0</v>
       </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1406,6 +1445,9 @@
       <c r="X6">
         <v>0</v>
       </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1480,6 +1522,9 @@
         <v>0</v>
       </c>
       <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
         <v>8</v>
       </c>
     </row>
@@ -1556,6 +1601,9 @@
         <v>0</v>
       </c>
       <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
         <v>1</v>
       </c>
     </row>
@@ -1634,6 +1682,9 @@
       <c r="X9">
         <v>0</v>
       </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1710,6 +1761,9 @@
       <c r="X10">
         <v>0</v>
       </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1784,6 +1838,9 @@
         <v>0</v>
       </c>
       <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
         <v>4</v>
       </c>
     </row>
@@ -1860,6 +1917,9 @@
         <v>0</v>
       </c>
       <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
         <v>2</v>
       </c>
     </row>
@@ -1936,6 +1996,9 @@
         <v>0</v>
       </c>
       <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
         <v>1</v>
       </c>
     </row>
@@ -2012,7 +2075,10 @@
         <v>1</v>
       </c>
       <c r="X14">
-        <v>119</v>
+        <v>7</v>
+      </c>
+      <c r="Y14">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2064,10 +2130,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2">
         <v>28</v>
@@ -2076,7 +2142,7 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3">
@@ -2328,10 +2394,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D14">
         <v>29</v>
@@ -2340,7 +2406,7 @@
         <v>23</v>
       </c>
       <c r="F14">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2350,7 +2416,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5044,6 +5110,160 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>10288</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>10033</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>10117</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>10516</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>10603</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -744,33 +744,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/07/26</t>
+          <t>08/05/26</t>
         </is>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
         <v>2</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/10/26</t>
+          <t>08/07/26</t>
         </is>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -782,20 +782,20 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/11/26</t>
+          <t>08/10/26</t>
         </is>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -804,17 +804,17 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/12/26</t>
+          <t>08/11/26</t>
         </is>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -823,20 +823,20 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/14/26</t>
+          <t>08/12/26</t>
         </is>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -854,11 +854,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/16/26</t>
+          <t>08/14/26</t>
         </is>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -867,23 +867,23 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/17/26</t>
+          <t>08/16/26</t>
         </is>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -892,29 +892,73 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B25">
+      <c r="B27">
         <v>30</v>
       </c>
-      <c r="C25">
-        <v>33</v>
-      </c>
-      <c r="D25">
-        <v>28</v>
-      </c>
-      <c r="E25">
+      <c r="C27">
+        <v>35</v>
+      </c>
+      <c r="D27">
+        <v>31</v>
+      </c>
+      <c r="E27">
         <v>18</v>
       </c>
-      <c r="F25">
-        <v>109</v>
+      <c r="F27">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +968,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1015,40 +1059,50 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>08/05/26</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>08/07/26</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>08/10/26</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>08/11/26</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>08/12/26</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>08/14/26</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>08/16/26</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>08/17/26</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1109,28 +1163,34 @@
         <v>1</v>
       </c>
       <c r="R2">
+        <v>2</v>
+      </c>
+      <c r="S2">
         <v>6</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>2</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>1</v>
-      </c>
-      <c r="U2">
-        <v>7</v>
       </c>
       <c r="V2">
         <v>7</v>
       </c>
       <c r="W2">
+        <v>7</v>
+      </c>
+      <c r="X2">
         <v>1</v>
       </c>
-      <c r="X2">
+      <c r="Y2">
         <v>7</v>
       </c>
-      <c r="Y2">
-        <v>109</v>
+      <c r="Z2">
+        <v>3</v>
+      </c>
+      <c r="AA2">
+        <v>114</v>
       </c>
     </row>
     <row r="3">
@@ -1209,6 +1269,12 @@
         <v>0</v>
       </c>
       <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
         <v>1</v>
       </c>
     </row>
@@ -1290,6 +1356,12 @@
       <c r="Y4">
         <v>0</v>
       </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1369,6 +1441,12 @@
       <c r="Y5">
         <v>0</v>
       </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1448,6 +1526,12 @@
       <c r="Y6">
         <v>0</v>
       </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1525,6 +1609,12 @@
         <v>0</v>
       </c>
       <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
         <v>8</v>
       </c>
     </row>
@@ -1604,6 +1694,12 @@
         <v>0</v>
       </c>
       <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
         <v>1</v>
       </c>
     </row>
@@ -1685,6 +1781,12 @@
       <c r="Y9">
         <v>0</v>
       </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1764,6 +1866,12 @@
       <c r="Y10">
         <v>0</v>
       </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1820,11 +1928,11 @@
         <v>0</v>
       </c>
       <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>1</v>
       </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
       <c r="T11">
         <v>0</v>
       </c>
@@ -1841,6 +1949,12 @@
         <v>0</v>
       </c>
       <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
         <v>4</v>
       </c>
     </row>
@@ -1920,6 +2034,12 @@
         <v>0</v>
       </c>
       <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
         <v>2</v>
       </c>
     </row>
@@ -1999,6 +2119,12 @@
         <v>0</v>
       </c>
       <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
         <v>1</v>
       </c>
     </row>
@@ -2057,28 +2183,34 @@
         <v>1</v>
       </c>
       <c r="R14">
+        <v>2</v>
+      </c>
+      <c r="S14">
         <v>7</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>2</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>1</v>
-      </c>
-      <c r="U14">
-        <v>7</v>
       </c>
       <c r="V14">
         <v>7</v>
       </c>
       <c r="W14">
+        <v>7</v>
+      </c>
+      <c r="X14">
         <v>1</v>
       </c>
-      <c r="X14">
+      <c r="Y14">
         <v>7</v>
       </c>
-      <c r="Y14">
-        <v>126</v>
+      <c r="Z14">
+        <v>3</v>
+      </c>
+      <c r="AA14">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2133,16 +2265,16 @@
         <v>30</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E2">
         <v>18</v>
       </c>
       <c r="F2">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
@@ -2397,16 +2529,16 @@
         <v>34</v>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E14">
         <v>23</v>
       </c>
       <c r="F14">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2416,7 +2548,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5264,6 +5396,116 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>10587</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>10070</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>08/05/26</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>10114</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>08/05/26</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>10014</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -942,23 +942,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B27">
-        <v>30</v>
-      </c>
-      <c r="C27">
+      <c r="B28">
+        <v>40</v>
+      </c>
+      <c r="C28">
         <v>35</v>
       </c>
-      <c r="D27">
+      <c r="D28">
         <v>31</v>
       </c>
-      <c r="E27">
+      <c r="E28">
         <v>18</v>
       </c>
-      <c r="F27">
-        <v>114</v>
+      <c r="F28">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +990,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1104,6 +1126,11 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1184,13 +1211,16 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z2">
         <v>3</v>
       </c>
       <c r="AA2">
-        <v>114</v>
+        <v>7</v>
+      </c>
+      <c r="AB2">
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -1275,6 +1305,9 @@
         <v>0</v>
       </c>
       <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -1362,6 +1395,9 @@
       <c r="AA4">
         <v>0</v>
       </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1447,6 +1483,9 @@
       <c r="AA5">
         <v>0</v>
       </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1532,6 +1571,9 @@
       <c r="AA6">
         <v>0</v>
       </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1615,7 +1657,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1700,6 +1745,9 @@
         <v>0</v>
       </c>
       <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -1787,6 +1835,9 @@
       <c r="AA9">
         <v>0</v>
       </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1872,6 +1923,9 @@
       <c r="AA10">
         <v>0</v>
       </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1955,6 +2009,9 @@
         <v>0</v>
       </c>
       <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
         <v>4</v>
       </c>
     </row>
@@ -2040,6 +2097,9 @@
         <v>0</v>
       </c>
       <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
         <v>2</v>
       </c>
     </row>
@@ -2125,6 +2185,9 @@
         <v>0</v>
       </c>
       <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -2204,13 +2267,16 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z14">
         <v>3</v>
       </c>
       <c r="AA14">
-        <v>131</v>
+        <v>8</v>
+      </c>
+      <c r="AB14">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2262,7 +2328,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>35</v>
@@ -2274,7 +2340,7 @@
         <v>18</v>
       </c>
       <c r="F2">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -2372,7 +2438,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2384,7 +2450,7 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2526,7 +2592,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C14">
         <v>42</v>
@@ -2538,7 +2604,7 @@
         <v>23</v>
       </c>
       <c r="F14">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2548,7 +2614,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5506,6 +5572,265 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>10025</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>10025</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>10157</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>10616</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>10615</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>10163</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>10212</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>10166</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>10643</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>10486</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>10216</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>08/17/26</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -365,25 +365,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JS</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>NB</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -399,15 +404,18 @@
         <v>0</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
     </row>
@@ -421,15 +429,18 @@
         <v>0</v>
       </c>
       <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>3</v>
       </c>
     </row>
@@ -443,15 +454,18 @@
         <v>0</v>
       </c>
       <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>5</v>
       </c>
     </row>
@@ -465,15 +479,18 @@
         <v>0</v>
       </c>
       <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
     </row>
@@ -487,15 +504,18 @@
         <v>0</v>
       </c>
       <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>
@@ -506,18 +526,21 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>8</v>
       </c>
     </row>
@@ -531,15 +554,18 @@
         <v>0</v>
       </c>
       <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>6</v>
       </c>
     </row>
@@ -556,12 +582,15 @@
         <v>0</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>6</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>2</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>8</v>
       </c>
     </row>
@@ -572,18 +601,21 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>3</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>4</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>8</v>
       </c>
     </row>
@@ -600,12 +632,15 @@
         <v>0</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>
@@ -619,15 +654,18 @@
         <v>0</v>
       </c>
       <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>3</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>3</v>
       </c>
     </row>
@@ -638,11 +676,11 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>7</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
       <c r="D13">
         <v>0</v>
       </c>
@@ -650,6 +688,9 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>7</v>
       </c>
     </row>
@@ -666,12 +707,15 @@
         <v>0</v>
       </c>
       <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
         <v>9</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>5</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>14</v>
       </c>
     </row>
@@ -685,15 +729,18 @@
         <v>0</v>
       </c>
       <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>3</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>3</v>
       </c>
     </row>
@@ -704,18 +751,21 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>3</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
       <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>4</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
       <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <v>7</v>
       </c>
     </row>
@@ -729,15 +779,18 @@
         <v>0</v>
       </c>
       <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <v>1</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
     </row>
@@ -754,12 +807,15 @@
         <v>0</v>
       </c>
       <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
         <v>2</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
       <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
         <v>2</v>
       </c>
     </row>
@@ -770,18 +826,21 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>4</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>2</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
         <v>6</v>
       </c>
     </row>
@@ -795,15 +854,18 @@
         <v>0</v>
       </c>
       <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
         <v>2</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>2</v>
       </c>
     </row>
@@ -814,11 +876,11 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>1</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
       <c r="D21">
         <v>0</v>
       </c>
@@ -826,6 +888,9 @@
         <v>0</v>
       </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>1</v>
       </c>
     </row>
@@ -836,19 +901,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22">
         <v>5</v>
       </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
-      <c r="F22">
-        <v>7</v>
+      <c r="G22">
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -867,11 +935,14 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>7</v>
       </c>
+      <c r="G23">
+        <v>7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -880,11 +951,11 @@
         </is>
       </c>
       <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
         <v>1</v>
       </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
       <c r="D24">
         <v>0</v>
       </c>
@@ -892,6 +963,9 @@
         <v>0</v>
       </c>
       <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
         <v>1</v>
       </c>
     </row>
@@ -902,18 +976,21 @@
         </is>
       </c>
       <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
         <v>6</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>4</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>10</v>
       </c>
     </row>
@@ -924,19 +1001,22 @@
         </is>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
         <v>2</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>1</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
       <c r="F26">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -946,11 +1026,11 @@
         </is>
       </c>
       <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
         <v>7</v>
       </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
       <c r="D27">
         <v>0</v>
       </c>
@@ -958,29 +1038,60 @@
         <v>0</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B28">
+      <c r="B29">
+        <v>14</v>
+      </c>
+      <c r="C29">
         <v>40</v>
       </c>
-      <c r="C28">
-        <v>35</v>
-      </c>
-      <c r="D28">
+      <c r="D29">
+        <v>38</v>
+      </c>
+      <c r="E29">
         <v>31</v>
       </c>
-      <c r="E28">
+      <c r="F29">
         <v>18</v>
       </c>
-      <c r="F28">
-        <v>124</v>
+      <c r="G29">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1131,6 +1242,11 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1202,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="V2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W2">
         <v>7</v>
@@ -1214,13 +1330,16 @@
         <v>10</v>
       </c>
       <c r="Z2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AA2">
         <v>7</v>
       </c>
       <c r="AB2">
-        <v>124</v>
+        <v>4</v>
+      </c>
+      <c r="AC2">
+        <v>141</v>
       </c>
     </row>
     <row r="3">
@@ -1308,6 +1427,9 @@
         <v>0</v>
       </c>
       <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <v>1</v>
       </c>
     </row>
@@ -1398,6 +1520,9 @@
       <c r="AB4">
         <v>0</v>
       </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1486,6 +1611,9 @@
       <c r="AB5">
         <v>0</v>
       </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1574,6 +1702,9 @@
       <c r="AB6">
         <v>0</v>
       </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1660,6 +1791,9 @@
         <v>1</v>
       </c>
       <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
         <v>9</v>
       </c>
     </row>
@@ -1748,6 +1882,9 @@
         <v>0</v>
       </c>
       <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
         <v>1</v>
       </c>
     </row>
@@ -1838,6 +1975,9 @@
       <c r="AB9">
         <v>0</v>
       </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1926,6 +2066,9 @@
       <c r="AB10">
         <v>0</v>
       </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2012,6 +2155,9 @@
         <v>0</v>
       </c>
       <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
         <v>4</v>
       </c>
     </row>
@@ -2100,6 +2246,9 @@
         <v>0</v>
       </c>
       <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
         <v>2</v>
       </c>
     </row>
@@ -2188,6 +2337,9 @@
         <v>0</v>
       </c>
       <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
         <v>1</v>
       </c>
     </row>
@@ -2258,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -2270,13 +2422,16 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>142</v>
+        <v>4</v>
+      </c>
+      <c r="AC14">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2286,7 +2441,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2297,25 +2452,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JS</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>NB</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2328,19 +2488,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>14</v>
+      </c>
+      <c r="C2">
         <v>40</v>
       </c>
-      <c r="C2">
-        <v>35</v>
-      </c>
       <c r="D2">
+        <v>38</v>
+      </c>
+      <c r="E2">
         <v>31</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>18</v>
       </c>
-      <c r="F2">
-        <v>124</v>
+      <c r="G2">
+        <v>141</v>
       </c>
     </row>
     <row r="3">
@@ -2359,11 +2522,14 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2386,6 +2552,9 @@
       <c r="F4">
         <v>0</v>
       </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2408,6 +2577,9 @@
       <c r="F5">
         <v>0</v>
       </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2430,6 +2602,9 @@
       <c r="F6">
         <v>0</v>
       </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2438,18 +2613,21 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>4</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>9</v>
       </c>
     </row>
@@ -2469,11 +2647,14 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2496,6 +2677,9 @@
       <c r="F9">
         <v>0</v>
       </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2518,6 +2702,9 @@
       <c r="F10">
         <v>0</v>
       </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2526,18 +2713,21 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>3</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>4</v>
       </c>
     </row>
@@ -2548,18 +2738,21 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
       <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>2</v>
       </c>
     </row>
@@ -2579,11 +2772,14 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2592,19 +2788,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>14</v>
+      </c>
+      <c r="C14">
         <v>45</v>
       </c>
-      <c r="C14">
-        <v>42</v>
-      </c>
       <c r="D14">
+        <v>45</v>
+      </c>
+      <c r="E14">
         <v>32</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>23</v>
       </c>
-      <c r="F14">
-        <v>142</v>
+      <c r="G14">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2614,7 +2813,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5831,6 +6030,397 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>10115</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>10059</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>10168</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>10310</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>10152</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>10221</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>10124</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>10248</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>10320</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>10260</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>10176</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>08/12/26</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>10243</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>10254</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>10051</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>10239</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>10094</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1072,26 +1072,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B30">
         <v>14</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>40</v>
       </c>
-      <c r="D29">
+      <c r="D30">
         <v>38</v>
       </c>
-      <c r="E29">
-        <v>31</v>
-      </c>
-      <c r="F29">
+      <c r="E30">
+        <v>32</v>
+      </c>
+      <c r="F30">
         <v>18</v>
       </c>
-      <c r="G29">
-        <v>141</v>
+      <c r="G30">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1101,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1247,6 +1272,11 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1339,7 +1369,10 @@
         <v>4</v>
       </c>
       <c r="AC2">
-        <v>141</v>
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -1430,6 +1463,9 @@
         <v>0</v>
       </c>
       <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
         <v>1</v>
       </c>
     </row>
@@ -1523,6 +1559,9 @@
       <c r="AC4">
         <v>0</v>
       </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1614,6 +1653,9 @@
       <c r="AC5">
         <v>0</v>
       </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1705,6 +1747,9 @@
       <c r="AC6">
         <v>0</v>
       </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1794,7 +1839,10 @@
         <v>0</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1885,6 +1933,9 @@
         <v>0</v>
       </c>
       <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
         <v>1</v>
       </c>
     </row>
@@ -1978,6 +2029,9 @@
       <c r="AC9">
         <v>0</v>
       </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2069,6 +2123,9 @@
       <c r="AC10">
         <v>0</v>
       </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2158,6 +2215,9 @@
         <v>0</v>
       </c>
       <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
         <v>4</v>
       </c>
     </row>
@@ -2249,6 +2309,9 @@
         <v>0</v>
       </c>
       <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
         <v>2</v>
       </c>
     </row>
@@ -2340,6 +2403,9 @@
         <v>0</v>
       </c>
       <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
         <v>1</v>
       </c>
     </row>
@@ -2431,7 +2497,10 @@
         <v>4</v>
       </c>
       <c r="AC14">
-        <v>159</v>
+        <v>2</v>
+      </c>
+      <c r="AD14">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2497,13 +2566,13 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>18</v>
       </c>
       <c r="G2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -2622,13 +2691,13 @@
         <v>4</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2797,13 +2866,13 @@
         <v>45</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14">
         <v>23</v>
       </c>
       <c r="G14">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2813,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6421,6 +6490,50 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>10296</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>10647</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1097,26 +1097,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>08/22/26</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>14</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>40</v>
       </c>
-      <c r="D30">
-        <v>38</v>
-      </c>
-      <c r="E30">
+      <c r="D31">
+        <v>40</v>
+      </c>
+      <c r="E31">
         <v>32</v>
       </c>
-      <c r="F30">
+      <c r="F31">
         <v>18</v>
       </c>
-      <c r="G30">
-        <v>142</v>
+      <c r="G31">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1126,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AE14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1277,6 +1302,11 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
+          <t>08/22/26</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1372,7 +1402,10 @@
         <v>1</v>
       </c>
       <c r="AD2">
-        <v>142</v>
+        <v>2</v>
+      </c>
+      <c r="AE2">
+        <v>144</v>
       </c>
     </row>
     <row r="3">
@@ -1466,6 +1499,9 @@
         <v>0</v>
       </c>
       <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
         <v>1</v>
       </c>
     </row>
@@ -1562,6 +1598,9 @@
       <c r="AD4">
         <v>0</v>
       </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1656,6 +1695,9 @@
       <c r="AD5">
         <v>0</v>
       </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1750,6 +1792,9 @@
       <c r="AD6">
         <v>0</v>
       </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1842,6 +1887,9 @@
         <v>1</v>
       </c>
       <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
         <v>10</v>
       </c>
     </row>
@@ -1936,6 +1984,9 @@
         <v>0</v>
       </c>
       <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
         <v>1</v>
       </c>
     </row>
@@ -2032,6 +2083,9 @@
       <c r="AD9">
         <v>0</v>
       </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2126,6 +2180,9 @@
       <c r="AD10">
         <v>0</v>
       </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2218,6 +2275,9 @@
         <v>0</v>
       </c>
       <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
         <v>4</v>
       </c>
     </row>
@@ -2312,6 +2372,9 @@
         <v>0</v>
       </c>
       <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
         <v>2</v>
       </c>
     </row>
@@ -2408,6 +2471,9 @@
       <c r="AD13">
         <v>1</v>
       </c>
+      <c r="AE13">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2500,7 +2566,10 @@
         <v>2</v>
       </c>
       <c r="AD14">
-        <v>161</v>
+        <v>3</v>
+      </c>
+      <c r="AE14">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2563,7 +2632,7 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2">
         <v>32</v>
@@ -2572,7 +2641,7 @@
         <v>18</v>
       </c>
       <c r="G2">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
@@ -2838,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -2847,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2863,7 +2932,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E14">
         <v>34</v>
@@ -2872,7 +2941,7 @@
         <v>23</v>
       </c>
       <c r="G14">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2882,7 +2951,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6534,6 +6603,72 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>10281</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>08/22/26</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>08/22/26</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Other Disposition (Please Describe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>10190</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>08/22/26</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -710,13 +710,13 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F14">
         <v>5</v>
       </c>
       <c r="G14">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -735,13 +735,13 @@
         <v>3</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -810,13 +810,13 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1010,13 +1010,13 @@
         <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -1035,13 +1035,13 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -1060,13 +1060,13 @@
         <v>3</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -1085,13 +1085,13 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -1122,26 +1122,51 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>8</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>14</v>
       </c>
-      <c r="C31">
-        <v>40</v>
-      </c>
-      <c r="D31">
-        <v>40</v>
-      </c>
-      <c r="E31">
-        <v>32</v>
-      </c>
-      <c r="F31">
+      <c r="C32">
+        <v>48</v>
+      </c>
+      <c r="D32">
+        <v>45</v>
+      </c>
+      <c r="E32">
+        <v>70</v>
+      </c>
+      <c r="F32">
         <v>18</v>
       </c>
-      <c r="G31">
-        <v>144</v>
+      <c r="G32">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -1151,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE14"/>
+  <dimension ref="A1:AF14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1307,6 +1332,11 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1354,19 +1384,19 @@
         <v>7</v>
       </c>
       <c r="N2">
+        <v>18</v>
+      </c>
+      <c r="O2">
+        <v>12</v>
+      </c>
+      <c r="P2">
         <v>14</v>
-      </c>
-      <c r="O2">
-        <v>3</v>
-      </c>
-      <c r="P2">
-        <v>7</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2">
         <v>6</v>
@@ -1390,22 +1420,25 @@
         <v>10</v>
       </c>
       <c r="Z2">
+        <v>13</v>
+      </c>
+      <c r="AA2">
         <v>10</v>
       </c>
-      <c r="AA2">
-        <v>7</v>
-      </c>
       <c r="AB2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD2">
         <v>2</v>
       </c>
       <c r="AE2">
-        <v>144</v>
+        <v>13</v>
+      </c>
+      <c r="AF2">
+        <v>195</v>
       </c>
     </row>
     <row r="3">
@@ -1502,6 +1535,9 @@
         <v>0</v>
       </c>
       <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
         <v>1</v>
       </c>
     </row>
@@ -1601,6 +1637,9 @@
       <c r="AE4">
         <v>0</v>
       </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1698,6 +1737,9 @@
       <c r="AE5">
         <v>0</v>
       </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1795,6 +1837,9 @@
       <c r="AE6">
         <v>0</v>
       </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1884,13 +1929,16 @@
         <v>0</v>
       </c>
       <c r="AC7">
+        <v>2</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
         <v>1</v>
       </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>10</v>
+      <c r="AF7">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1987,6 +2035,9 @@
         <v>0</v>
       </c>
       <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
         <v>1</v>
       </c>
     </row>
@@ -2086,6 +2137,9 @@
       <c r="AE9">
         <v>0</v>
       </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2183,6 +2237,9 @@
       <c r="AE10">
         <v>0</v>
       </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2278,6 +2335,9 @@
         <v>0</v>
       </c>
       <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
         <v>4</v>
       </c>
     </row>
@@ -2375,6 +2435,9 @@
         <v>0</v>
       </c>
       <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
         <v>2</v>
       </c>
     </row>
@@ -2472,6 +2535,9 @@
         <v>1</v>
       </c>
       <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
         <v>2</v>
       </c>
     </row>
@@ -2518,19 +2584,19 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q14">
         <v>1</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S14">
         <v>7</v>
@@ -2554,22 +2620,25 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA14">
+        <v>11</v>
+      </c>
+      <c r="AB14">
+        <v>9</v>
+      </c>
+      <c r="AC14">
         <v>8</v>
-      </c>
-      <c r="AB14">
-        <v>4</v>
-      </c>
-      <c r="AC14">
-        <v>2</v>
       </c>
       <c r="AD14">
         <v>3</v>
       </c>
       <c r="AE14">
-        <v>164</v>
+        <v>14</v>
+      </c>
+      <c r="AF14">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2629,19 +2698,19 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="F2">
         <v>18</v>
       </c>
       <c r="G2">
-        <v>144</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3">
@@ -2754,19 +2823,19 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -2929,19 +2998,19 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E14">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="F14">
         <v>23</v>
       </c>
       <c r="G14">
-        <v>164</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2951,7 +3020,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6669,6 +6738,1172 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>10671</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>10200</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>10282</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>10094</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>10040</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>08/05/26</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>10042</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>10073</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>10086</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>07/30/26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>10229</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>07/31/26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>10021</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>07/31/26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>10126</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>07/30/26</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>10142</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>07/30/26</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>10214</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>10095</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>07/30/26</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>07/31/26</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>10184</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>07/30/26</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>10065</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>07/31/26</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>10214</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>10222</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>10155</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>07/30/26</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>07/31/26</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>10085</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>10664</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>07/30/26</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>10186</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>07/30/26</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>10047</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>07/31/26</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>10653</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>10060</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>08/19/26</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>07/31/26</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>10123</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>10006</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>08/20/26</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>10013</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>08/18/26</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>10608</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>10476</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>10241</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>08/05/26</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>10271</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>07/30/26</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>10648</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>10648</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>08/21/26</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>10599</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>10173</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>10294</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>10605</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>10193</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>10044</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>10269</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>10261</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>10613</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>10120</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>10122</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>10298</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>10036</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>08/24/26</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1147,26 +1147,51 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>08/25/26</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>14</v>
       </c>
-      <c r="C32">
-        <v>48</v>
-      </c>
-      <c r="D32">
+      <c r="C33">
+        <v>49</v>
+      </c>
+      <c r="D33">
         <v>45</v>
       </c>
-      <c r="E32">
+      <c r="E33">
         <v>70</v>
       </c>
-      <c r="F32">
+      <c r="F33">
         <v>18</v>
       </c>
-      <c r="G32">
-        <v>195</v>
+      <c r="G33">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -1176,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF14"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1337,6 +1362,11 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
+          <t>08/25/26</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1438,7 +1468,10 @@
         <v>13</v>
       </c>
       <c r="AF2">
-        <v>195</v>
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>196</v>
       </c>
     </row>
     <row r="3">
@@ -1538,6 +1571,9 @@
         <v>0</v>
       </c>
       <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
         <v>1</v>
       </c>
     </row>
@@ -1640,6 +1676,9 @@
       <c r="AF4">
         <v>0</v>
       </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1740,6 +1779,9 @@
       <c r="AF5">
         <v>0</v>
       </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1840,6 +1882,9 @@
       <c r="AF6">
         <v>0</v>
       </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1938,6 +1983,9 @@
         <v>1</v>
       </c>
       <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
         <v>12</v>
       </c>
     </row>
@@ -2038,6 +2086,9 @@
         <v>0</v>
       </c>
       <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
         <v>1</v>
       </c>
     </row>
@@ -2140,6 +2191,9 @@
       <c r="AF9">
         <v>0</v>
       </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2240,6 +2294,9 @@
       <c r="AF10">
         <v>0</v>
       </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2338,6 +2395,9 @@
         <v>0</v>
       </c>
       <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
         <v>4</v>
       </c>
     </row>
@@ -2438,6 +2498,9 @@
         <v>0</v>
       </c>
       <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
         <v>2</v>
       </c>
     </row>
@@ -2538,6 +2601,9 @@
         <v>0</v>
       </c>
       <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
         <v>2</v>
       </c>
     </row>
@@ -2638,7 +2704,10 @@
         <v>14</v>
       </c>
       <c r="AF14">
-        <v>217</v>
+        <v>1</v>
+      </c>
+      <c r="AG14">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2698,7 +2767,7 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2">
         <v>45</v>
@@ -2710,7 +2779,7 @@
         <v>18</v>
       </c>
       <c r="G2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3">
@@ -2998,7 +3067,7 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14">
         <v>53</v>
@@ -3010,7 +3079,7 @@
         <v>23</v>
       </c>
       <c r="G14">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3020,7 +3089,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7904,6 +7973,28 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>10062</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>08/25/26</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1172,26 +1172,51 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>9</v>
+      </c>
+      <c r="G33">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>14</v>
       </c>
-      <c r="C33">
-        <v>49</v>
-      </c>
-      <c r="D33">
-        <v>45</v>
-      </c>
-      <c r="E33">
+      <c r="C34">
+        <v>51</v>
+      </c>
+      <c r="D34">
+        <v>48</v>
+      </c>
+      <c r="E34">
         <v>70</v>
       </c>
-      <c r="F33">
-        <v>18</v>
-      </c>
-      <c r="G33">
-        <v>196</v>
+      <c r="F34">
+        <v>27</v>
+      </c>
+      <c r="G34">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -1201,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AH14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1367,6 +1392,11 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1471,7 +1501,10 @@
         <v>1</v>
       </c>
       <c r="AG2">
-        <v>196</v>
+        <v>14</v>
+      </c>
+      <c r="AH2">
+        <v>210</v>
       </c>
     </row>
     <row r="3">
@@ -1576,6 +1609,9 @@
       <c r="AG3">
         <v>1</v>
       </c>
+      <c r="AH3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1677,7 +1713,10 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1782,6 +1821,9 @@
       <c r="AG5">
         <v>0</v>
       </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1885,6 +1927,9 @@
       <c r="AG6">
         <v>0</v>
       </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1986,6 +2031,9 @@
         <v>0</v>
       </c>
       <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
         <v>12</v>
       </c>
     </row>
@@ -2089,6 +2137,9 @@
         <v>0</v>
       </c>
       <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
         <v>1</v>
       </c>
     </row>
@@ -2194,6 +2245,9 @@
       <c r="AG9">
         <v>0</v>
       </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2297,6 +2351,9 @@
       <c r="AG10">
         <v>0</v>
       </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2398,7 +2455,10 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="AH11">
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -2501,6 +2561,9 @@
         <v>0</v>
       </c>
       <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
         <v>2</v>
       </c>
     </row>
@@ -2604,6 +2667,9 @@
         <v>0</v>
       </c>
       <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
         <v>2</v>
       </c>
     </row>
@@ -2707,7 +2773,10 @@
         <v>1</v>
       </c>
       <c r="AG14">
-        <v>218</v>
+        <v>18</v>
+      </c>
+      <c r="AH14">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -2767,19 +2836,19 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E2">
         <v>70</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>196</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3">
@@ -2801,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2826,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2992,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -3004,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -3067,19 +3136,19 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E14">
         <v>73</v>
       </c>
       <c r="F14">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G14">
-        <v>218</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3089,7 +3158,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:D243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7995,6 +8064,419 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>10138</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>10293</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Eligible, Asked to Leave Before Audit Started - Permission Not Given</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>10112</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>10327</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>10089</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>10058</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>10604</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>10309</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Eligible, Asked to Leave During Audit - Audit Partially Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>10218</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>10649</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>10075</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>10127</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>10078</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>10245</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>10082</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>10118</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>10600</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1197,26 +1197,51 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>14</v>
       </c>
-      <c r="C34">
+      <c r="C35">
+        <v>54</v>
+      </c>
+      <c r="D35">
         <v>51</v>
       </c>
-      <c r="D34">
-        <v>48</v>
-      </c>
-      <c r="E34">
+      <c r="E35">
         <v>70</v>
       </c>
-      <c r="F34">
+      <c r="F35">
         <v>27</v>
       </c>
-      <c r="G34">
-        <v>210</v>
+      <c r="G35">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -1226,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH14"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,6 +1422,11 @@
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1504,7 +1534,10 @@
         <v>14</v>
       </c>
       <c r="AH2">
-        <v>210</v>
+        <v>6</v>
+      </c>
+      <c r="AI2">
+        <v>216</v>
       </c>
     </row>
     <row r="3">
@@ -1610,6 +1643,9 @@
         <v>1</v>
       </c>
       <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
         <v>2</v>
       </c>
     </row>
@@ -1716,6 +1752,9 @@
         <v>1</v>
       </c>
       <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
         <v>1</v>
       </c>
     </row>
@@ -1824,6 +1863,9 @@
       <c r="AH5">
         <v>0</v>
       </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1930,6 +1972,9 @@
       <c r="AH6">
         <v>0</v>
       </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2034,6 +2079,9 @@
         <v>0</v>
       </c>
       <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
         <v>12</v>
       </c>
     </row>
@@ -2140,6 +2188,9 @@
         <v>0</v>
       </c>
       <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
         <v>1</v>
       </c>
     </row>
@@ -2248,6 +2299,9 @@
       <c r="AH9">
         <v>0</v>
       </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2354,6 +2408,9 @@
       <c r="AH10">
         <v>0</v>
       </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2458,7 +2515,10 @@
         <v>2</v>
       </c>
       <c r="AH11">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2564,6 +2624,9 @@
         <v>0</v>
       </c>
       <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
         <v>2</v>
       </c>
     </row>
@@ -2670,6 +2733,9 @@
         <v>0</v>
       </c>
       <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
         <v>2</v>
       </c>
     </row>
@@ -2776,7 +2842,10 @@
         <v>18</v>
       </c>
       <c r="AH14">
-        <v>236</v>
+        <v>7</v>
+      </c>
+      <c r="AI14">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -2836,10 +2905,10 @@
         <v>14</v>
       </c>
       <c r="C2">
+        <v>54</v>
+      </c>
+      <c r="D2">
         <v>51</v>
-      </c>
-      <c r="D2">
-        <v>48</v>
       </c>
       <c r="E2">
         <v>70</v>
@@ -2848,7 +2917,7 @@
         <v>27</v>
       </c>
       <c r="G2">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3">
@@ -3064,7 +3133,7 @@
         <v>3</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -3073,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -3136,10 +3205,10 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>73</v>
@@ -3148,7 +3217,7 @@
         <v>34</v>
       </c>
       <c r="G14">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -3158,7 +3227,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D243"/>
+  <dimension ref="A1:D250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8477,6 +8546,160 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>10026</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>10046</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>10219</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>10667</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Ineligible-Does Not Sell Tobacco or Nicotine</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>10140</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1222,26 +1222,51 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>14</v>
       </c>
-      <c r="C35">
-        <v>54</v>
-      </c>
-      <c r="D35">
+      <c r="C36">
+        <v>55</v>
+      </c>
+      <c r="D36">
         <v>51</v>
       </c>
-      <c r="E35">
+      <c r="E36">
         <v>70</v>
       </c>
-      <c r="F35">
+      <c r="F36">
         <v>27</v>
       </c>
-      <c r="G35">
-        <v>216</v>
+      <c r="G36">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -1251,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI14"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1427,6 +1452,11 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1537,7 +1567,10 @@
         <v>6</v>
       </c>
       <c r="AI2">
-        <v>216</v>
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>217</v>
       </c>
     </row>
     <row r="3">
@@ -1646,6 +1679,9 @@
         <v>0</v>
       </c>
       <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
         <v>2</v>
       </c>
     </row>
@@ -1755,6 +1791,9 @@
         <v>0</v>
       </c>
       <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
         <v>1</v>
       </c>
     </row>
@@ -1866,6 +1905,9 @@
       <c r="AI5">
         <v>0</v>
       </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1975,6 +2017,9 @@
       <c r="AI6">
         <v>0</v>
       </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2082,6 +2127,9 @@
         <v>0</v>
       </c>
       <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
         <v>12</v>
       </c>
     </row>
@@ -2191,6 +2239,9 @@
         <v>0</v>
       </c>
       <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
         <v>1</v>
       </c>
     </row>
@@ -2302,6 +2353,9 @@
       <c r="AI9">
         <v>0</v>
       </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2411,6 +2465,9 @@
       <c r="AI10">
         <v>0</v>
       </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2518,6 +2575,9 @@
         <v>1</v>
       </c>
       <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
         <v>7</v>
       </c>
     </row>
@@ -2627,6 +2687,9 @@
         <v>0</v>
       </c>
       <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
         <v>2</v>
       </c>
     </row>
@@ -2736,6 +2799,9 @@
         <v>0</v>
       </c>
       <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
         <v>2</v>
       </c>
     </row>
@@ -2845,7 +2911,10 @@
         <v>7</v>
       </c>
       <c r="AI14">
-        <v>243</v>
+        <v>1</v>
+      </c>
+      <c r="AJ14">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -2905,7 +2974,7 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2">
         <v>51</v>
@@ -2917,7 +2986,7 @@
         <v>27</v>
       </c>
       <c r="G2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
@@ -3205,7 +3274,7 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14">
         <v>60</v>
@@ -3217,7 +3286,7 @@
         <v>34</v>
       </c>
       <c r="G14">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3227,7 +3296,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D250"/>
+  <dimension ref="A1:D252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8700,6 +8769,45 @@
         </is>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>10097</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1247,26 +1247,51 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>08/29/26</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>14</v>
       </c>
-      <c r="C36">
+      <c r="C37">
         <v>55</v>
       </c>
-      <c r="D36">
-        <v>51</v>
-      </c>
-      <c r="E36">
+      <c r="D37">
+        <v>53</v>
+      </c>
+      <c r="E37">
         <v>70</v>
       </c>
-      <c r="F36">
+      <c r="F37">
         <v>27</v>
       </c>
-      <c r="G36">
-        <v>217</v>
+      <c r="G37">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1457,6 +1482,11 @@
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
+          <t>08/29/26</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1570,7 +1600,10 @@
         <v>1</v>
       </c>
       <c r="AJ2">
-        <v>217</v>
+        <v>2</v>
+      </c>
+      <c r="AK2">
+        <v>219</v>
       </c>
     </row>
     <row r="3">
@@ -1682,6 +1715,9 @@
         <v>0</v>
       </c>
       <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
         <v>2</v>
       </c>
     </row>
@@ -1794,6 +1830,9 @@
         <v>0</v>
       </c>
       <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
         <v>1</v>
       </c>
     </row>
@@ -1908,6 +1947,9 @@
       <c r="AJ5">
         <v>0</v>
       </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2020,6 +2062,9 @@
       <c r="AJ6">
         <v>0</v>
       </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2130,6 +2175,9 @@
         <v>0</v>
       </c>
       <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
         <v>12</v>
       </c>
     </row>
@@ -2242,6 +2290,9 @@
         <v>0</v>
       </c>
       <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
         <v>1</v>
       </c>
     </row>
@@ -2356,6 +2407,9 @@
       <c r="AJ9">
         <v>0</v>
       </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2468,6 +2522,9 @@
       <c r="AJ10">
         <v>0</v>
       </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2578,6 +2635,9 @@
         <v>0</v>
       </c>
       <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
         <v>7</v>
       </c>
     </row>
@@ -2690,6 +2750,9 @@
         <v>0</v>
       </c>
       <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
         <v>2</v>
       </c>
     </row>
@@ -2802,6 +2865,9 @@
         <v>0</v>
       </c>
       <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
         <v>2</v>
       </c>
     </row>
@@ -2914,7 +2980,10 @@
         <v>1</v>
       </c>
       <c r="AJ14">
-        <v>244</v>
+        <v>2</v>
+      </c>
+      <c r="AK14">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -2977,7 +3046,7 @@
         <v>55</v>
       </c>
       <c r="D2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2">
         <v>70</v>
@@ -2986,7 +3055,7 @@
         <v>27</v>
       </c>
       <c r="G2">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
@@ -3277,7 +3346,7 @@
         <v>63</v>
       </c>
       <c r="D14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14">
         <v>73</v>
@@ -3286,7 +3355,7 @@
         <v>34</v>
       </c>
       <c r="G14">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -3296,7 +3365,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D252"/>
+  <dimension ref="A1:D254"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8808,6 +8877,50 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>08/29/26</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>10601</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>08/29/26</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1272,26 +1272,51 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>14</v>
       </c>
-      <c r="C37">
+      <c r="C38">
+        <v>58</v>
+      </c>
+      <c r="D38">
         <v>55</v>
       </c>
-      <c r="D37">
-        <v>53</v>
-      </c>
-      <c r="E37">
+      <c r="E38">
         <v>70</v>
       </c>
-      <c r="F37">
+      <c r="F38">
         <v>27</v>
       </c>
-      <c r="G37">
-        <v>219</v>
+      <c r="G38">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -1301,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AL14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1487,6 +1512,11 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1597,13 +1627,16 @@
         <v>6</v>
       </c>
       <c r="AI2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ2">
         <v>2</v>
       </c>
       <c r="AK2">
-        <v>219</v>
+        <v>3</v>
+      </c>
+      <c r="AL2">
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -1718,6 +1751,9 @@
         <v>0</v>
       </c>
       <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
         <v>2</v>
       </c>
     </row>
@@ -1833,6 +1869,9 @@
         <v>0</v>
       </c>
       <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
         <v>1</v>
       </c>
     </row>
@@ -1950,6 +1989,9 @@
       <c r="AK5">
         <v>0</v>
       </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2065,6 +2107,9 @@
       <c r="AK6">
         <v>0</v>
       </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2172,13 +2217,16 @@
         <v>0</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2293,6 +2341,9 @@
         <v>0</v>
       </c>
       <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
         <v>1</v>
       </c>
     </row>
@@ -2410,6 +2461,9 @@
       <c r="AK9">
         <v>0</v>
       </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2525,6 +2579,9 @@
       <c r="AK10">
         <v>0</v>
       </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2638,6 +2695,9 @@
         <v>0</v>
       </c>
       <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
         <v>7</v>
       </c>
     </row>
@@ -2753,6 +2813,9 @@
         <v>0</v>
       </c>
       <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
         <v>2</v>
       </c>
     </row>
@@ -2868,6 +2931,9 @@
         <v>0</v>
       </c>
       <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
         <v>2</v>
       </c>
     </row>
@@ -2977,13 +3043,16 @@
         <v>7</v>
       </c>
       <c r="AI14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ14">
         <v>2</v>
       </c>
       <c r="AK14">
-        <v>246</v>
+        <v>3</v>
+      </c>
+      <c r="AL14">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3043,10 +3112,10 @@
         <v>14</v>
       </c>
       <c r="C2">
+        <v>58</v>
+      </c>
+      <c r="D2">
         <v>55</v>
-      </c>
-      <c r="D2">
-        <v>53</v>
       </c>
       <c r="E2">
         <v>70</v>
@@ -3055,7 +3124,7 @@
         <v>27</v>
       </c>
       <c r="G2">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -3168,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -3180,7 +3249,7 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -3343,10 +3412,10 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E14">
         <v>73</v>
@@ -3355,7 +3424,7 @@
         <v>34</v>
       </c>
       <c r="G14">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3365,7 +3434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D254"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8921,6 +8990,155 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>10275</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>10147</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>10161</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>10161</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>10090</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>10349</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1213,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1297,26 +1297,51 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>6</v>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>14</v>
       </c>
-      <c r="C38">
-        <v>58</v>
-      </c>
-      <c r="D38">
+      <c r="C39">
+        <v>62</v>
+      </c>
+      <c r="D39">
         <v>55</v>
       </c>
-      <c r="E38">
+      <c r="E39">
         <v>70</v>
       </c>
-      <c r="F38">
-        <v>27</v>
-      </c>
-      <c r="G38">
-        <v>224</v>
+      <c r="F39">
+        <v>34</v>
+      </c>
+      <c r="G39">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -1326,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL14"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1517,6 +1542,11 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>Sum</t>
         </is>
       </c>
@@ -1624,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="AH2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI2">
         <v>3</v>
@@ -1636,7 +1666,10 @@
         <v>3</v>
       </c>
       <c r="AL2">
-        <v>224</v>
+        <v>10</v>
+      </c>
+      <c r="AM2">
+        <v>235</v>
       </c>
     </row>
     <row r="3">
@@ -1754,6 +1787,9 @@
         <v>0</v>
       </c>
       <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
         <v>2</v>
       </c>
     </row>
@@ -1872,6 +1908,9 @@
         <v>0</v>
       </c>
       <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>1</v>
       </c>
     </row>
@@ -1992,6 +2031,9 @@
       <c r="AL5">
         <v>0</v>
       </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2110,6 +2152,9 @@
       <c r="AL6">
         <v>0</v>
       </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2226,7 +2271,10 @@
         <v>0</v>
       </c>
       <c r="AL7">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="AM7">
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -2344,6 +2392,9 @@
         <v>0</v>
       </c>
       <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>1</v>
       </c>
     </row>
@@ -2464,6 +2515,9 @@
       <c r="AL9">
         <v>0</v>
       </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2582,6 +2636,9 @@
       <c r="AL10">
         <v>0</v>
       </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2698,6 +2755,9 @@
         <v>0</v>
       </c>
       <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
         <v>7</v>
       </c>
     </row>
@@ -2816,6 +2876,9 @@
         <v>0</v>
       </c>
       <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>2</v>
       </c>
     </row>
@@ -2934,7 +2997,10 @@
         <v>0</v>
       </c>
       <c r="AL13">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="AM13">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3040,7 +3106,7 @@
         <v>18</v>
       </c>
       <c r="AH14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI14">
         <v>4</v>
@@ -3052,7 +3118,10 @@
         <v>3</v>
       </c>
       <c r="AL14">
-        <v>252</v>
+        <v>13</v>
+      </c>
+      <c r="AM14">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3112,7 +3181,7 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D2">
         <v>55</v>
@@ -3121,10 +3190,10 @@
         <v>70</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3">
@@ -3243,13 +3312,13 @@
         <v>4</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -3396,10 +3465,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3412,19 +3481,19 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D14">
         <v>64</v>
       </c>
       <c r="E14">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F14">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G14">
-        <v>252</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3434,7 +3503,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D275"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9139,6 +9208,314 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>10233</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>10211</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>10213</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>08/27/26</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>10632</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>10227</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Other Disposition (Please Describe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>10116</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>10342</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>10228</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>10085</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>10058</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>10353</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>09/01/26</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/audits_report.xlsx
+++ b/audits_report.xlsx
@@ -1185,13 +1185,13 @@
         <v>3</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>9</v>
       </c>
       <c r="G33">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1235,13 +1235,13 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -1260,13 +1260,13 @@
         <v>2</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1285,13 +1285,13 @@
         <v>2</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1335,13 +1335,13 @@
         <v>55</v>
       </c>
       <c r="E39">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F39">
         <v>34</v>
       </c>
       <c r="G39">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -1651,25 +1651,25 @@
         <v>1</v>
       </c>
       <c r="AG2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH2">
         <v>7</v>
       </c>
       <c r="AI2">
+        <v>5</v>
+      </c>
+      <c r="AJ2">
         <v>3</v>
       </c>
-      <c r="AJ2">
-        <v>2</v>
-      </c>
       <c r="AK2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AL2">
         <v>10</v>
       </c>
       <c r="AM2">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL7">
         <v>2</v>
       </c>
       <c r="AM7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -3103,25 +3103,25 @@
         <v>1</v>
       </c>
       <c r="AG14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH14">
         <v>8</v>
       </c>
       <c r="AI14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AL14">
         <v>13</v>
       </c>
       <c r="AM14">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3187,13 +3187,13 @@
         <v>55</v>
       </c>
       <c r="E2">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F2">
         <v>34</v>
       </c>
       <c r="G2">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
@@ -3312,13 +3312,13 @@
         <v>4</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -3487,13 +3487,13 @@
         <v>64</v>
       </c>
       <c r="E14">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F14">
         <v>43</v>
       </c>
       <c r="G14">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3503,7 +3503,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D275"/>
+  <dimension ref="A1:D285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -9516,6 +9516,226 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>10087</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Not Attempted, Permanently Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>10308</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>10175</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>10291</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>10161</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>10138</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>08/26/26</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>10366</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>08/31/26</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>10280</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>08/29/26</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>10097</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>08/28/26</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Eligible, Audit Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
